--- a/data/trans_camb/P1435_2011_2023-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P1435_2011_2023-Estudios-trans_camb.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2,0</t>
+          <t>1,88</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>7,38</t>
+          <t>6,85</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5,25</t>
+          <t>4,82</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,88; 3,56</t>
+          <t>0,69; 3,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,16; 9,99</t>
+          <t>4,87; 8,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,97; 7,07</t>
+          <t>3,55; 6,22</t>
         </is>
       </c>
     </row>
@@ -594,17 +594,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>378,54%</t>
+          <t>354,29%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>195,25%</t>
+          <t>181,23%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>217,85%</t>
+          <t>200,14%</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>71,45; 1678,82</t>
+          <t>59,63; 1341,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>108,86; 311,1</t>
+          <t>107,39; 291,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>135,56; 341,88</t>
+          <t>122,84; 310,66</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1,13</t>
+          <t>1,18</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>12,96</t>
+          <t>5,09</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7,05</t>
+          <t>3,18</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,6; 1,83</t>
+          <t>0,62; 1,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,16; 36,73</t>
+          <t>3,72; 6,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,48; 22,5</t>
+          <t>2,41; 3,94</t>
         </is>
       </c>
     </row>
@@ -690,17 +690,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>462,05%</t>
+          <t>482,46%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>386,87%</t>
+          <t>152,04%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>411,59%</t>
+          <t>185,53%</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>109,14; 1670,74</t>
+          <t>105,94; 1549,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>116,95; 1301,87</t>
+          <t>90,57; 240,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>138,67; 1543,75</t>
+          <t>117,6; 290,91</t>
         </is>
       </c>
     </row>
@@ -740,17 +740,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1,65</t>
+          <t>1,74</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4,89</t>
+          <t>4,59</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3,34</t>
+          <t>3,26</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,7; 3,08</t>
+          <t>0,77; 3,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,05; 7,39</t>
+          <t>1,79; 7,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,94; 4,74</t>
+          <t>1,86; 4,6</t>
         </is>
       </c>
     </row>
@@ -786,17 +786,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>758,43%</t>
+          <t>798,71%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>129,48%</t>
+          <t>121,74%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>171,26%</t>
+          <t>166,72%</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>31,87; 305,29</t>
+          <t>31,18; 299,94</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>61,04; 368,18</t>
+          <t>60,96; 368,3</t>
         </is>
       </c>
     </row>
@@ -836,17 +836,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>1,32</t>
+          <t>1,37</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>10,3</t>
+          <t>5,34</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5,95</t>
+          <t>3,43</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,76; 1,89</t>
+          <t>0,92; 1,94</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,92; 26,9</t>
+          <t>4,26; 6,33</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,0; 16,35</t>
+          <t>2,86; 4,04</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>409,31%</t>
+          <t>425,82%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>288,82%</t>
+          <t>149,86%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>301,13%</t>
+          <t>173,56%</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>154,39; 930,97</t>
+          <t>178,08; 1026,68</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>129,94; 836,71</t>
+          <t>99,37; 205,67</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>146,65; 829,53</t>
+          <t>124,83; 231,18</t>
         </is>
       </c>
     </row>
